--- a/2026/SAENZ PEÑA/Marzo/SAENZ_EXPENSAS-Marzo.xlsx
+++ b/2026/SAENZ PEÑA/Marzo/SAENZ_EXPENSAS-Marzo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SAENZ PEÑA\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFB9E6D-4137-4CE4-9B41-D60A87938AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9F4042-71EA-46E3-A135-2D1E72DD1E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
   <si>
     <t>UF</t>
   </si>
@@ -253,7 +253,10 @@
     <t xml:space="preserve">  </t>
   </si>
   <si>
-    <t xml:space="preserve">adma - Contactor modular Bipolar </t>
+    <t xml:space="preserve">ADMA - Contactor modular Bipolar </t>
+  </si>
+  <si>
+    <t>Destapacion - Forlini Nora</t>
   </si>
 </sst>
 </file>
@@ -268,7 +271,7 @@
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,13 +379,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1072,7 +1068,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1347,8 +1343,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1716,7 +1710,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1808,7 +1802,7 @@
         <v>48</v>
       </c>
       <c r="F12" s="121">
-        <v>1714239.3492361403</v>
+        <v>1870625.3392361405</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1827,7 +1821,7 @@
       </c>
       <c r="F13" s="50">
         <f>'prorrateo '!F11</f>
-        <v>408115.52</v>
+        <v>312200</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1837,7 +1831,7 @@
       <c r="B14" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="149">
+      <c r="C14" s="105">
         <v>42663.94</v>
       </c>
       <c r="D14" s="5"/>
@@ -1845,8 +1839,8 @@
         <v>22</v>
       </c>
       <c r="F14" s="50">
-        <f>-(C36)</f>
-        <v>-288427.73</v>
+        <f>-(C37)</f>
+        <v>-372041.53</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1868,7 +1862,7 @@
         <v>70</v>
       </c>
       <c r="B16" s="97"/>
-      <c r="C16" s="148">
+      <c r="C16" s="71">
         <v>10568</v>
       </c>
       <c r="D16" s="5"/>
@@ -1890,7 +1884,7 @@
       </c>
       <c r="F17" s="118">
         <f>SUM(F12:F15)</f>
-        <v>1833927.1392361405</v>
+        <v>1810783.8092361402</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1903,7 +1897,7 @@
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="97" t="s">
         <v>42</v>
       </c>
@@ -1911,176 +1905,183 @@
         <v>73</v>
       </c>
       <c r="C19" s="71">
-        <f xml:space="preserve"> 69942+69942*10%</f>
-        <v>76936.2</v>
+        <v>88800</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="97" t="s">
         <v>75</v>
       </c>
       <c r="B20" s="104"/>
-      <c r="C20" s="148">
+      <c r="C20" s="71">
         <v>37824.480000000003</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="97" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B21" s="104"/>
-      <c r="C21" s="105">
-        <v>48250</v>
+      <c r="C21" s="71">
+        <v>120000</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="97" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="104"/>
-      <c r="C22" s="105"/>
+      <c r="C22" s="105">
+        <v>0</v>
+      </c>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="102"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="119">
-        <f>SUM(C18:C22)</f>
-        <v>163010.68</v>
-      </c>
+      <c r="A23" s="97" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="104"/>
+      <c r="C23" s="105"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="6"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="102"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="119">
+        <f>SUM(C18:C23)</f>
+        <v>246624.48</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="120">
-        <f>+C23+C17</f>
-        <v>288427.73</v>
-      </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20"/>
-    </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="73"/>
-      <c r="C25" s="74"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="120">
+        <f>+C24+C17</f>
+        <v>372041.53</v>
+      </c>
+      <c r="D25" s="5"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="60" t="s">
         <v>27</v>
       </c>
+      <c r="B26" s="73"/>
+      <c r="C26" s="74"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
     </row>
     <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="46"/>
-      <c r="F27" s="6"/>
+      <c r="A27" s="22" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="45">
-        <v>0</v>
-      </c>
+      <c r="A28" s="37"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="46"/>
       <c r="F28" s="6"/>
     </row>
     <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="52"/>
-      <c r="B29" s="53"/>
+      <c r="A29" s="44"/>
+      <c r="B29" s="43"/>
       <c r="C29" s="45">
         <v>0</v>
       </c>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="69"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="72"/>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="52"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="45">
+        <v>0</v>
+      </c>
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="69"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="77"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="72"/>
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="69"/>
-      <c r="B32" s="75"/>
-      <c r="C32" s="72">
-        <v>0</v>
-      </c>
+      <c r="B32" s="76"/>
+      <c r="C32" s="77"/>
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="69"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="72">
+        <v>0</v>
+      </c>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="56">
-        <f>SUM(C28:C32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B34" s="55"/>
+      <c r="C34" s="56">
+        <f>SUM(C29:C33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="122">
-        <f>C24-C22</f>
-        <v>288427.73</v>
-      </c>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+      <c r="C35" s="122">
+        <f>C25-C23</f>
+        <v>372041.53</v>
+      </c>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="123">
-        <f>+C24</f>
-        <v>288427.73</v>
-      </c>
-      <c r="E35" s="100"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="54" t="s">
+      <c r="C36" s="123">
+        <f>+C25</f>
+        <v>372041.53</v>
+      </c>
+      <c r="E36" s="100"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="55"/>
-      <c r="C36" s="124">
-        <f>C34</f>
-        <v>288427.73</v>
-      </c>
-      <c r="E36" s="16"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D41" s="6"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="124">
+        <f>C35</f>
+        <v>372041.53</v>
+      </c>
+      <c r="E37" s="16"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D43" s="16"/>
@@ -2088,19 +2089,18 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D45" s="16"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="20"/>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D46" s="16"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="18"/>
+      <c r="A58" s="19"/>
       <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
+      <c r="C58" s="20"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="18"/>
@@ -2131,6 +2131,11 @@
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2187,7 +2192,7 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="62">
-        <v>250000</v>
+        <v>372041.53</v>
       </c>
       <c r="L1" s="27"/>
     </row>
@@ -2292,23 +2297,25 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>564587.30400625931</v>
-      </c>
-      <c r="F5" s="71"/>
+        <v>649812.63754278515</v>
+      </c>
+      <c r="F5" s="127">
+        <v>100000</v>
+      </c>
       <c r="G5" s="58">
         <f>E5-F5</f>
-        <v>564587.30400625931</v>
+        <v>549812.63754278515</v>
       </c>
       <c r="H5" s="61">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>47425.333536525788</v>
+        <v>46184.261553593955</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="31">
         <f>K1*D5</f>
-        <v>37800</v>
+        <v>56252.679336000001</v>
       </c>
       <c r="K5" s="15">
         <f>K2*D5</f>
@@ -2316,7 +2323,7 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>649812.63754278515</v>
+        <v>652249.57843237906</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -2333,11 +2340,11 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>62760.000000000007</v>
+        <v>39225</v>
       </c>
       <c r="F6" s="127">
         <f>E6</f>
-        <v>62760.000000000007</v>
+        <v>39225</v>
       </c>
       <c r="G6" s="58">
         <f t="shared" ref="G6:G8" si="0">E6-F6</f>
@@ -2352,7 +2359,7 @@
       </c>
       <c r="J6" s="31">
         <f>K1*D6</f>
-        <v>39225</v>
+        <v>58373.316057000011</v>
       </c>
       <c r="K6" s="15">
         <f>K2*D6</f>
@@ -2360,7 +2367,7 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>39225</v>
+        <v>58373.316057000011</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -2377,11 +2384,11 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>131875.52000000002</v>
+        <v>39550</v>
       </c>
       <c r="F7" s="127">
         <f>E7</f>
-        <v>131875.52000000002</v>
+        <v>39550</v>
       </c>
       <c r="G7" s="58">
         <f t="shared" si="0"/>
@@ -2396,7 +2403,7 @@
       </c>
       <c r="J7" s="31">
         <f>K1*D7</f>
-        <v>39550</v>
+        <v>58856.970046000009</v>
       </c>
       <c r="K7" s="15">
         <f>K2*D7</f>
@@ -2404,7 +2411,7 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="2">J7+K7+H7+G7</f>
-        <v>39550</v>
+        <v>58856.970046000009</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -2421,11 +2428,11 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="E8" s="34">
-        <v>79200</v>
+        <v>49500</v>
       </c>
       <c r="F8" s="127">
         <f>E8</f>
-        <v>79200</v>
+        <v>49500</v>
       </c>
       <c r="G8" s="58">
         <f t="shared" si="0"/>
@@ -2440,7 +2447,7 @@
       </c>
       <c r="J8" s="31">
         <f>K1*D8</f>
-        <v>49500</v>
+        <v>73664.222940000007</v>
       </c>
       <c r="K8" s="15">
         <f>K2*D8</f>
@@ -2448,7 +2455,7 @@
       </c>
       <c r="L8" s="32">
         <f t="shared" si="2"/>
-        <v>49500</v>
+        <v>73664.222940000007</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -2465,11 +2472,11 @@
         <v>0.15920000000000001</v>
       </c>
       <c r="E9" s="34">
-        <v>63680</v>
+        <v>39800</v>
       </c>
       <c r="F9" s="127">
         <f>E9</f>
-        <v>63680</v>
+        <v>39800</v>
       </c>
       <c r="G9" s="58">
         <f>E9-F9</f>
@@ -2484,7 +2491,7 @@
       </c>
       <c r="J9" s="31">
         <f>K1*D9</f>
-        <v>39800</v>
+        <v>59229.011576000004</v>
       </c>
       <c r="K9" s="15">
         <f>K2*D9</f>
@@ -2492,7 +2499,7 @@
       </c>
       <c r="L9" s="32">
         <f t="shared" si="2"/>
-        <v>39800</v>
+        <v>59229.011576000004</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -2509,11 +2516,11 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>70600</v>
+        <v>44125</v>
       </c>
       <c r="F10" s="127">
         <f>E10</f>
-        <v>70600</v>
+        <v>44125</v>
       </c>
       <c r="G10" s="58">
         <f>E10-F10</f>
@@ -2528,7 +2535,7 @@
       </c>
       <c r="J10" s="31">
         <f>K1*D10</f>
-        <v>44125</v>
+        <v>65665.330044999995</v>
       </c>
       <c r="K10" s="15">
         <f>K2*D10</f>
@@ -2536,7 +2543,7 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>44125</v>
+        <v>65665.330044999995</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2551,19 +2558,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="3">SUM(E5:E10)</f>
-        <v>972702.82400625932</v>
+        <v>862012.63754278515</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>408115.52</v>
+        <v>312200</v>
       </c>
       <c r="G11" s="42">
         <f>SUM(G5:G10)</f>
-        <v>564587.30400625931</v>
+        <v>549812.63754278515</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" ref="H11:K11" si="4">SUM(H5:H10)</f>
-        <v>47425.333536525788</v>
+        <v>46184.261553593955</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="4"/>
@@ -2571,7 +2578,7 @@
       </c>
       <c r="J11" s="39">
         <f t="shared" si="4"/>
-        <v>250000</v>
+        <v>372041.53</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="4"/>
@@ -2579,7 +2586,7 @@
       </c>
       <c r="L11" s="42">
         <f>SUM(L5:L10)</f>
-        <v>862012.63754278515</v>
+        <v>968038.42909637897</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
